--- a/artfynd/A 35437-2022 artfynd.xlsx
+++ b/artfynd/A 35437-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 35437-2022 artfynd.xlsx
+++ b/artfynd/A 35437-2022 artfynd.xlsx
@@ -3947,7 +3947,7 @@
         <v>116969763</v>
       </c>
       <c r="B30" t="n">
-        <v>57278</v>
+        <v>57478</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ånge (Ånge), Jmt</t>
+          <t>Ånge, Ånge, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
@@ -12042,7 +12042,7 @@
         <v>116971093</v>
       </c>
       <c r="B100" t="n">
-        <v>57278</v>
+        <v>57478</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12080,7 +12080,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Ånge (Ånge), Jmt</t>
+          <t>Ånge, Ånge, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
@@ -12164,7 +12164,7 @@
         <v>116971265</v>
       </c>
       <c r="B101" t="n">
-        <v>57278</v>
+        <v>57478</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>

--- a/artfynd/A 35437-2022 artfynd.xlsx
+++ b/artfynd/A 35437-2022 artfynd.xlsx
@@ -3951,7 +3951,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -12046,7 +12046,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">

--- a/artfynd/A 35437-2022 artfynd.xlsx
+++ b/artfynd/A 35437-2022 artfynd.xlsx
@@ -3947,7 +3947,7 @@
         <v>116969763</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -12042,7 +12042,7 @@
         <v>116971093</v>
       </c>
       <c r="B100" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>116971265</v>
       </c>
       <c r="B101" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>

--- a/artfynd/A 35437-2022 artfynd.xlsx
+++ b/artfynd/A 35437-2022 artfynd.xlsx
@@ -3947,7 +3947,7 @@
         <v>116969763</v>
       </c>
       <c r="B30" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -12042,7 +12042,7 @@
         <v>116971093</v>
       </c>
       <c r="B100" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>116971265</v>
       </c>
       <c r="B101" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>

--- a/artfynd/A 35437-2022 artfynd.xlsx
+++ b/artfynd/A 35437-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY116"/>
+  <dimension ref="A1:AZ116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109442382</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -867,6 +877,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109466512</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -964,6 +979,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109466460</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1061,6 +1081,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109466461</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1158,6 +1183,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109466462</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1255,6 +1285,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109466463</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1352,6 +1387,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109466464</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1460,6 +1500,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112831294</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1567,6 +1612,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116970125</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1674,6 +1724,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116970378</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1781,6 +1836,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116970715</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1883,6 +1943,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109472369</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1990,6 +2055,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116970027</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2098,6 +2168,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103240402</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2200,6 +2275,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109441948</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2297,6 +2377,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109466508</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2405,6 +2490,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112831241</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2517,6 +2607,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103240388</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2615,6 +2710,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109442283</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2713,6 +2813,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109443004</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2810,6 +2915,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109466482</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2907,6 +3017,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109466483</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3004,6 +3119,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109466484</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3101,6 +3221,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109466485</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3213,6 +3338,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103240361</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3321,6 +3451,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103240676</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3419,6 +3554,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109442177</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3516,6 +3656,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109466478</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3613,6 +3758,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109466475</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3721,6 +3871,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112830650</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3838,6 +3993,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116969416</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3950,6 +4110,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116969763</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4067,6 +4232,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116971093</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4187,6 +4357,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116971265</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4309,6 +4484,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103240625</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4423,6 +4603,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103240284</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4545,6 +4730,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103165700</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4654,6 +4844,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103165992</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4776,6 +4971,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103240263</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4894,6 +5094,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103240420</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5003,6 +5208,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103240473</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5112,6 +5322,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103240519</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5230,6 +5445,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103240562</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5339,6 +5559,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103240609</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5448,6 +5673,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103240681</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5557,6 +5787,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103240700</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5666,6 +5901,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103240729</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5775,6 +6015,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103240878</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5884,6 +6129,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103241009</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5993,6 +6243,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103241048</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6102,6 +6357,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103241097</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6211,6 +6471,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103241110</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6320,6 +6585,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103241547</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6429,6 +6699,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103241560</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6538,6 +6813,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103257142</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6640,6 +6920,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109466488</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6742,6 +7027,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109466489</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6844,6 +7134,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109466490</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6946,6 +7241,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109466491</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7048,6 +7348,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109466492</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7150,6 +7455,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109466493</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7252,6 +7562,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109466494</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7354,6 +7669,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109466495</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7456,6 +7776,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109466497</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7558,6 +7883,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109466498</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7660,6 +7990,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109466499</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7762,6 +8097,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109466500</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7864,6 +8204,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109466501</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7966,6 +8311,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109466502</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8068,6 +8418,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109466503</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8170,6 +8525,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109466504</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8272,6 +8632,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109466505</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8374,6 +8739,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109466506</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8491,6 +8861,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112830777</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8608,6 +8983,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112830817</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8725,6 +9105,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112831300</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8842,6 +9227,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112831480</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8958,6 +9348,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116969907</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9074,6 +9469,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116970002</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9190,6 +9590,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116970662</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9306,6 +9711,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116970691</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9422,6 +9832,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116970761</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9538,6 +9953,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116971108</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9654,6 +10074,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116971439</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9751,6 +10176,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109466469</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9848,6 +10278,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109466470</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9945,6 +10380,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109466471</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10042,6 +10482,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109466472</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10139,6 +10584,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109466473</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10236,6 +10686,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109466481</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10333,6 +10788,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109466507</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10435,6 +10895,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109441031</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10537,6 +11002,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109439677</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10639,6 +11109,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109440012</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10741,6 +11216,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109478331</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10849,6 +11329,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103241254</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10947,6 +11432,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109444559</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11055,6 +11545,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112831081</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11153,6 +11648,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109444630</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11261,6 +11761,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112831106</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11368,6 +11873,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109444684</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11475,6 +11985,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109444519</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11582,6 +12097,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109439713</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11689,6 +12209,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109444029</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11797,6 +12322,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112830994</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11906,6 +12436,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103241204</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12024,6 +12559,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103241353</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12137,6 +12677,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103241386</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12246,6 +12791,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103241441</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12364,6 +12914,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103257036</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12466,6 +13021,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109443854</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12568,6 +13128,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109466496</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12685,6 +13250,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112830847</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12802,6 +13372,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112830999</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12900,8 +13475,130 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109444663</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>